--- a/sample_templates/Update_Farmer_Number_Data.xlsx
+++ b/sample_templates/Update_Farmer_Number_Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,16 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>value_4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>value_5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>value_6</t>
         </is>
       </c>
     </row>

--- a/sample_templates/Update_Farmer_Number_Data.xlsx
+++ b/sample_templates/Update_Farmer_Number_Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,26 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>value_6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>value_7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>value_8</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>value_9</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>value_10</t>
         </is>
       </c>
     </row>
